--- a/khurana_cv/data/cv_entries.xlsx
+++ b/khurana_cv/data/cv_entries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havis\University of Oregon Dropbox\Havi Khurana\Personal\Coding projects\khurana_cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89943AFA-6928-4069-BEC5-950AA6E9BC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEEAEB0-7B52-4F01-8C1D-B4B5C655061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
   <si>
     <t>type</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>award</t>
-  </si>
-  <si>
-    <t>Expected 2025</t>
   </si>
   <si>
     <t>M.S. Economics</t>
@@ -303,18 +300,64 @@
 Advisor: Prof. David Liebowitz</t>
   </si>
   <si>
-    <t>GPA: 4.12
+    <t>Worked with Dr. David Liebowitz on research projects exploring principle effects and school discipline</t>
+  </si>
+  <si>
+    <t>Worked with Dr. Gina Biancarosa and Dr. Patrick Kennedy on research projects related to Dynamic Indicators of Basic Early Literacy Skill (DIBELS8) reading assessments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National R&amp;D Center to Improve Education for Secondary English Learners </t>
+  </si>
+  <si>
+    <t>Worked with Prof. Ilana Umansky and Prof. Karen Thompson on integrated ELD programs in Oregon</t>
+  </si>
+  <si>
+    <t>Summer 2022/23/24/25; Winter/Spring 2026</t>
+  </si>
+  <si>
+    <t>Fall 2025</t>
+  </si>
+  <si>
+    <t>Summer Graduate Student Fellowship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Society for Research on Educational Effectiveness (SREE) </t>
+  </si>
+  <si>
+    <t>Collaborated with iMentor to document participant engagement in the college mentoring program</t>
+  </si>
+  <si>
+    <t>6380</t>
+  </si>
+  <si>
+    <t>GPA: 4.22
 Advisor: Prof. Glen Waddell
-Thesis Title: Student First, or Budget First? Examining School Districts’ Spending Trends for Special Education Students.</t>
-  </si>
-  <si>
-    <t>Worked with Dr. David Liebowitz on research projects exploring principle effects and school discipline</t>
-  </si>
-  <si>
-    <t>Worked with Dr. Gina Biancarosa and Dr. Patrick Kennedy on research projects related to Dynamic Indicators of Basic Early Literacy Skill (DIBELS8) reading assessments</t>
-  </si>
-  <si>
-    <t>Composite Percentage: 87% (equivalent to a GPA of 4)</t>
+Thesis Title: Optimal Special Education Identification Under State Finance Policies</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Golden </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Egg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Innovator Awards</t>
+    </r>
+  </si>
+  <si>
+    <t>Awarded for holding a patent on reading assessment</t>
   </si>
 </sst>
 </file>
@@ -336,6 +379,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -435,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -474,6 +518,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1634,7 +1679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.5" style="1" customWidth="1"/>
@@ -1665,7 +1710,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>5</v>
@@ -1674,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17.149999999999999" customHeight="1">
@@ -1685,20 +1730,20 @@
         <v>2021</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>9</v>
@@ -1711,18 +1756,18 @@
       <c r="B3" s="2">
         <v>2022</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="2">
+        <v>2025</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="22" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="4" t="s">
@@ -1740,15 +1785,13 @@
         <v>2017</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="23" t="s">
-        <v>89</v>
-      </c>
+      <c r="G4" s="23"/>
       <c r="H4" s="5"/>
       <c r="I4" s="4" t="s">
         <v>9</v>
@@ -1758,21 +1801,19 @@
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2">
-        <v>2021</v>
-      </c>
-      <c r="C5" s="2">
-        <v>2024</v>
-      </c>
+      <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="4" t="s">
@@ -1783,47 +1824,45 @@
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
-        <v>2022</v>
-      </c>
-      <c r="C6" s="2">
-        <v>2024</v>
-      </c>
+      <c r="B6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>79</v>
+      <c r="E6" t="s">
+        <v>87</v>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="24" t="s">
         <v>88</v>
       </c>
       <c r="H6" s="5"/>
-      <c r="I6" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="2">
         <v>2021</v>
       </c>
-      <c r="C7" s="5">
-        <v>2025</v>
+      <c r="C7" s="2">
+        <v>2024</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1831,48 +1870,48 @@
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2">
-        <v>2019</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B8" s="12">
         <v>2021</v>
       </c>
+      <c r="C8" s="5">
+        <v>2025</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="5"/>
+        <v>44</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>14</v>
+      <c r="B9" s="2">
+        <v>2019</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2021</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="17.149999999999999" customHeight="1">
@@ -1880,20 +1919,20 @@
         <v>10</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
@@ -1903,68 +1942,68 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="6" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9" t="s">
-        <v>47</v>
+        <v>12</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>55</v>
+        <v>27</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -1974,20 +2013,20 @@
         <v>16</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -1997,61 +2036,59 @@
         <v>16</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>52</v>
+      <c r="D15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>55</v>
       </c>
       <c r="H15" s="5"/>
-      <c r="I15" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="34" customHeight="1">
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="5">
-        <v>3600</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>40</v>
+      <c r="B16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17.149999999999999" customHeight="1">
+    <row r="17" spans="1:9" ht="34" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C17" s="11"/>
-      <c r="D17" s="14" t="s">
-        <v>35</v>
+      <c r="D17" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>8</v>
@@ -2060,7 +2097,7 @@
         <v>3600</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="s">
@@ -2076,16 +2113,16 @@
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>52</v>
+        <v>34</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="F18" s="5">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
@@ -2096,24 +2133,26 @@
       <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="2">
         <v>2022</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="F19" s="5">
-        <v>300</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>57</v>
+        <v>3000</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A20" s="4" t="s">
@@ -2124,14 +2163,16 @@
       </c>
       <c r="C20" s="11"/>
       <c r="D20" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="F20" s="5">
+        <v>300</v>
+      </c>
       <c r="G20" s="10" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -2141,69 +2182,67 @@
         <v>16</v>
       </c>
       <c r="B21" s="5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="5">
-        <v>6000</v>
-      </c>
-      <c r="G21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="17.149999999999999" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C22" s="11"/>
+      <c r="D22" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17.149999999999999" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2">
         <v>2017</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="16" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" ht="16" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="12">
-        <v>2024</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="12">
-        <v>700</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="11"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="16" customHeight="1">
       <c r="A24" s="13" t="s">
@@ -2213,16 +2252,16 @@
         <v>2024</v>
       </c>
       <c r="C24" s="11"/>
-      <c r="D24" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>58</v>
+      <c r="D24" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="F24" s="12">
-        <v>3500</v>
-      </c>
-      <c r="G24" s="13" t="s">
+        <v>700</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="11"/>
@@ -2237,13 +2276,15 @@
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="12">
+        <v>3500</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>65</v>
       </c>
       <c r="H25" s="11"/>
@@ -2251,27 +2292,127 @@
     </row>
     <row r="26" spans="1:9" ht="16" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="B26" s="12">
         <v>2024</v>
       </c>
       <c r="C26" s="11"/>
-      <c r="D26" s="11" t="s">
-        <v>84</v>
+      <c r="D26" s="18" t="s">
+        <v>62</v>
       </c>
       <c r="E26" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+    </row>
+    <row r="27" spans="1:9" ht="16" customHeight="1">
+      <c r="A27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="12">
+        <v>2024</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="11">
+        <v>10000</v>
+      </c>
+      <c r="G27" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="11">
-        <v>10000</v>
-      </c>
-      <c r="G26" s="13" t="s">
+      <c r="H27" s="11"/>
+      <c r="I27" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="16" customHeight="1">
+      <c r="A28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="12">
+        <v>2025</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="11">
+        <v>8000</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="16" customHeight="1">
+      <c r="A29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="12">
+        <v>2025</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="20" t="s">
-        <v>9</v>
+      <c r="E29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:9" ht="16" customHeight="1">
+      <c r="A30" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="12">
+        <v>2025</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="5">
+        <v>3000</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="16" customHeight="1">
+      <c r="A31" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="12">
+        <v>2025</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
